--- a/data/raw/김포 25년/항공통계상세조회(노선) (9).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (9).xlsx
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10759</t>
-  </si>
-  <si>
-    <t>1968281</t>
-  </si>
-  <si>
-    <t>15610</t>
+    <t>5380</t>
+  </si>
+  <si>
+    <t>989309</t>
+  </si>
+  <si>
+    <t>8094</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,172 +53,172 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>479</t>
-  </si>
-  <si>
-    <t>76571</t>
-  </si>
-  <si>
-    <t>728</t>
+    <t>240</t>
+  </si>
+  <si>
+    <t>39468</t>
+  </si>
+  <si>
+    <t>377</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>6474</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>686</t>
+  </si>
+  <si>
+    <t>104390</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>9207</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5573</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>82949</t>
+  </si>
+  <si>
+    <t>2067</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>10183</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>6645</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>9862</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>9970</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>10867</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3375</t>
+  </si>
+  <si>
+    <t>656744</t>
+  </si>
+  <si>
+    <t>4340</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1699</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>13353</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1372</t>
-  </si>
-  <si>
-    <t>207821</t>
-  </si>
-  <si>
-    <t>748</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>19081</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>11103</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>719</t>
-  </si>
-  <si>
-    <t>159632</t>
-  </si>
-  <si>
-    <t>2892</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>21373</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>13612</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>19038</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>20473</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>22304</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6748</t>
-  </si>
-  <si>
-    <t>1308683</t>
-  </si>
-  <si>
-    <t>9164</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>15488</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>3354</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>56395</t>
-  </si>
-  <si>
-    <t>904</t>
+    <t>27278</t>
+  </si>
+  <si>
+    <t>315</t>
   </si>
 </sst>
 </file>
